--- a/光伏配储项目/电价数据/2026/陶博站.xlsx
+++ b/光伏配储项目/电价数据/2026/陶博站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51152</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76474</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57484</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60605</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52197</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5202100000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44433</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13188</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10707</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11302</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13617</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11361</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14698</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.07088999999999999</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09168000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01624</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10447</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15382</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21737</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.20794</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24818</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10447</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.21848</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21756</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.66944</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55971</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.39748</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41378</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.63317</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44779</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58241</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.64755</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.83201</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6441699999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.66037</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8161499999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.23665</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6966599999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60381</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8615900000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65801</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.66731</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65884</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.62971</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48127</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42578</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71408</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.75962</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.52683</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.85223</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5349299999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5184800000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50512</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51117</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46968</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6008600000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7408899999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52712</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.07081</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.51058</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77199</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.25143</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.81628</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5430499999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14562</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.52826</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.44199</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.65911</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.80283</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.64851</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70363</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7901699999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7465700000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.68667</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6109600000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7771</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.60145</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46172</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06335</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47596</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66655</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43807</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51727</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53952</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.22563</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.51564</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48095</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52203</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49339</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17279</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.53189</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.49808</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.57992</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57798</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6511699999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.76117</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57548</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5438500000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49627</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42526</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40928</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34238</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46076</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.24449</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22721</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.18711</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.11027</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10754</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17854</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19265</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.23924</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5420900000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07432999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13437</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24325</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21973</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23863</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20369</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12222</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.66047</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30005</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25933</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05226</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04042</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05286</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04459</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04825</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03588</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04614</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04414</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04647</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0433</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04433</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21822</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04093</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05525</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04739</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.02091</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15981</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11599</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35064</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68138</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04593</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09941</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00389</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04324</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04414</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04767</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20005</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33548</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31771</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27111</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17104</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15953</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2141</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22666</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45571</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79092</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810900000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92057</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49468</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91577</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86664</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29879</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8918200000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63251</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19139</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87093</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54187</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33517</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03593</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53504</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7945099999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5296000000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77655</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7803600000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87721</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8757200000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49646</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4042</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21131</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87903</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62614</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5394099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58574</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42713</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5957100000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6018600000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66289</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47541</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58245</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8809600000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63186</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.88095</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86348</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86619</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.47034</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41445</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9196299999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46498</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49905</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19903</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19452</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43224</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44772</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5950700000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33209</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13919</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69857</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78895</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6450199999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57801</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49935</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42715</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43322</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49483</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.19144</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63451</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25049</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.21179</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69931</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.43925</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.8162999999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57869</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46204</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7516499999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3235</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.37121</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>1.18306</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.16513</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1.15262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.16347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.28855</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>1.16824</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>1.29732</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>1.16249</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23241</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1.13541</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.13768</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.21319</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16187</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16706</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44263</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34843</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5368999999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20281</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24953</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24227</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35984</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49812</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44198</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.95472</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.76619</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.90307</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12656</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70938</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5333600000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28483</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6519400000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77383</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45747</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34366</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.43184</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20142</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22451</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.93251</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.82999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.8251799999999999</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.57899</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8260299999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.81388</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6483099999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60529</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67261</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82535</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43041</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.08822</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35977</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48958</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53843</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49438</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44713</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49885</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47526</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.66508</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46831</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40657</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6553099999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.23184</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5449700000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69555</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.72864</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67379</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8119700000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5925499999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52379</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83053</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77059</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6282000000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67487</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48185</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47656</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4679</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43345</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44478</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45353</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04817</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46176</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11914</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18023</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.00559</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36473</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22632</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26954</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13923</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04301</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18378</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34944</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25187</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03064</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04881</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11489</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01875</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03879</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00771</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03337</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02888</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02229</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01854</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18837</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00149</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04869</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03365</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04846</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18369</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19267</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25961</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12478</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.56472</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25398</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26426</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24069</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22926</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24777</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21234</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24034</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24287</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27235</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21887</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14336</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62905</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60593</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57996</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15803</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11696</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23569</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17736</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10718</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11718</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06848</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09970999999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01581</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.03074</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16906</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02747</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10843</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11917</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13816</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02211</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09061</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10447</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10264</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14194</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.46925</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32304</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.57673</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5589500000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47965</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14276</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50345</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32831</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62614</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.58868</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5112599999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49653</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50673</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48927</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.62609</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45519</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36753</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48198</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47432</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27886</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5546</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.43047</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.51419</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51576</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5833200000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5865900000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5278200000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51083</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5536799999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51916</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.69799</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86602</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58373</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58327</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44188</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37233</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25757</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22902</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16325</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07626000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.23152</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04447</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22188</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17724</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01194</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17373</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06044</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08091</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16287</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42603</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35969</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8656900000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47078</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42528</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25756</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24974</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11444</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.26411</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00394</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04861</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02029</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04842</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23846</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.09633</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.09992</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.2864</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.32097</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.34762</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.33463</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58027</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35933</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61503</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45514</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25796</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20588</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22948</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11425</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15028</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04657</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04686999999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07854999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03004</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06304999999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09678</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17034</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.1959</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12049</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22955</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12406</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05533</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26241</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14635</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11736</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23663</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18503</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20332</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27395</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36605</v>
       </c>
     </row>
   </sheetData>
